--- a/informes/informe_seguimiento_emilio_rivas_audi.xlsx
+++ b/informes/informe_seguimiento_emilio_rivas_audi.xlsx
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -252,6 +252,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3057,7 +3060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3073,367 +3076,615 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
+          <t>Proactividad comercial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Abr 2026</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Desgaste total (%)</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B5" s="26" t="n">
         <v>252.57</v>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C5" s="27" t="n">
         <v>264.34</v>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>220%</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Posición ranking</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B6" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Var Rec 2A (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>≥0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Var MO 2A (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>≥0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>ICC Proactividad</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>ICC Digital</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>CAL1SEM</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B17" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>5,0</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>ICC Calidad</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Procesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Productividad (%)</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B22" s="26" t="n">
         <v>90.72</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>92.45</v>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Var Rec 2A (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Var MO 2A (%)</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>41.38</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Recursos generales</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>ICC Recursos</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Carrocería</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>ICC Carrocería</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>ICC Personas</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Rankings de marca</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>ICC posición global</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>Horch Lauden</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B39" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C39" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D39" s="28" t="inlineStr">
         <is>
           <t>≤50</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>ICC posición global</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>ICC Proactividad</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>ICC Digital</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>ICC Calidad</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>ICC Recursos</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>ICC Carrocería</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>ICC Personas</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>ONE KVPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>Score ONE</t>
         </is>
       </c>
-      <c r="B18" s="25" t="n">
+      <c r="B43" s="26" t="n">
         <v>6.3</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C43" s="27" t="n">
         <v>6.8</v>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>7,3</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>Service CAM (%)</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B44" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C44" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D44" s="28" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>Diferidos (%)</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B45" s="26" t="n">
         <v>23</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C45" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>Multimedia</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B46" s="30" t="n">
         <v>6.6</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C46" s="27" t="n">
         <v>6.8</v>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3462,36 +3713,36 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>Objetivo de productividad específico para esta instalación: 93%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Positivo si...</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Mejorar si...</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Desgaste total (%)</t>
         </is>
@@ -3501,19 +3752,19 @@
           <t>&gt;220%</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>≥220%</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>&lt;220% — seguimiento prioritario</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>CAL1SEM</t>
         </is>
@@ -3523,19 +3774,19 @@
           <t>≥5,0</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>≥5,0</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>&lt;5,0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Productividad</t>
         </is>
@@ -3545,19 +3796,19 @@
           <t>Específico por instalación</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>≥objetivo</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>&lt;objetivo</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Var Rec 2A</t>
         </is>
@@ -3567,19 +3818,19 @@
           <t>≥0%</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>≥0%</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>&lt;0%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Var MO 2A</t>
         </is>
@@ -3589,19 +3840,19 @@
           <t>≥0%</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>≥0%</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>&lt;0%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Horch Lauden (pos)</t>
         </is>
@@ -3611,19 +3862,19 @@
           <t>≤50 aceptable</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>≤20 dest. / ≤50 acept.</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>&gt;50 — requiere atención</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>ONE Score SEM</t>
         </is>
@@ -3633,19 +3884,19 @@
           <t>Por encima de la media (7,3)</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>&gt;7,3</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>≤7,3</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>ONE Service CAM</t>
         </is>
@@ -3655,19 +3906,19 @@
           <t>≥8%</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>≥8%</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>5-8% regular / &lt;5% mejorar</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>ONE Diferidos</t>
         </is>
@@ -3677,19 +3928,19 @@
           <t>≥8%</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>≥8%</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>5-8% regular / &lt;5% mejorar</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>ONE Multimedia</t>
         </is>
@@ -3699,12 +3950,12 @@
           <t>≥5</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>≥5</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>3-5 regular / &lt;3 mejorar</t>
         </is>

--- a/informes/informe_seguimiento_emilio_rivas_audi.xlsx
+++ b/informes/informe_seguimiento_emilio_rivas_audi.xlsx
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>220%</t>
+          <t>&gt;220%</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>≥0%</t>
+          <t>&gt;8%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>≥0%</t>
+          <t>&gt;6%</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="D17" s="28" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>≥6</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D39" s="28" t="inlineStr">
         <is>
-          <t>≤50</t>
+          <t>&lt;20</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D45" s="28" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>

--- a/informes/informe_seguimiento_emilio_rivas_audi.xlsx
+++ b/informes/informe_seguimiento_emilio_rivas_audi.xlsx
@@ -3060,7 +3060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3575,7 +3575,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>ONE KVPS</t>
+          <t>Cuadro CX</t>
         </is>
       </c>
     </row>
@@ -3604,78 +3604,128 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
+          <t>CX total (/8)</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="inlineStr">
+        <is>
+          <t>≥7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>ONE KVPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
           <t>Score ONE</t>
         </is>
       </c>
-      <c r="B43" s="26" t="n">
+      <c r="B47" s="26" t="n">
         <v>6.3</v>
       </c>
-      <c r="C43" s="27" t="n">
+      <c r="C47" s="27" t="n">
         <v>6.8</v>
       </c>
-      <c r="D43" s="28" t="inlineStr">
+      <c r="D47" s="28" t="inlineStr">
         <is>
           <t>7,3</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="29" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>Service CAM (%)</t>
         </is>
       </c>
-      <c r="B44" s="30" t="n">
+      <c r="B48" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C44" s="27" t="n">
+      <c r="C48" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="D44" s="28" t="inlineStr">
+      <c r="D48" s="28" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>Diferidos (%)</t>
         </is>
       </c>
-      <c r="B45" s="26" t="n">
+      <c r="B49" s="26" t="n">
         <v>23</v>
       </c>
-      <c r="C45" s="27" t="n">
+      <c r="C49" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="D45" s="28" t="inlineStr">
+      <c r="D49" s="28" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="29" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>Multimedia</t>
         </is>
       </c>
-      <c r="B46" s="30" t="n">
+      <c r="B50" s="30" t="n">
         <v>6.6</v>
       </c>
-      <c r="C46" s="27" t="n">
+      <c r="C50" s="27" t="n">
         <v>6.8</v>
       </c>
-      <c r="D46" s="28" t="inlineStr">
+      <c r="D50" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>

--- a/informes/informe_seguimiento_emilio_rivas_audi.xlsx
+++ b/informes/informe_seguimiento_emilio_rivas_audi.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar 20261" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abr 2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolución" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objetivos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,14 +97,8 @@
       <color rgb="00FFD700"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="008B6914"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -147,21 +140,6 @@
         <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -189,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -285,21 +263,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3738,284 +3701,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Objetivos y umbrales de referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
-        <is>
-          <t>Objetivo de productividad específico para esta instalación: 93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Referencia</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>Positivo si...</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Mejorar si...</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>Desgaste total (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>&gt;220%</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>≥220%</t>
-        </is>
-      </c>
-      <c r="D6" s="37" t="inlineStr">
-        <is>
-          <t>&lt;220% — seguimiento prioritario</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="38" t="inlineStr">
-        <is>
-          <t>CAL1SEM</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>≥5,0</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>≥5,0</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="inlineStr">
-        <is>
-          <t>&lt;5,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>Productividad</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Específico por instalación</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>≥objetivo</t>
-        </is>
-      </c>
-      <c r="D8" s="37" t="inlineStr">
-        <is>
-          <t>&lt;objetivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
-        <is>
-          <t>Var Rec 2A</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="inlineStr">
-        <is>
-          <t>&lt;0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>Var MO 2A</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="D10" s="37" t="inlineStr">
-        <is>
-          <t>&lt;0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>Horch Lauden (pos)</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>≤50 aceptable</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>≤20 dest. / ≤50 acept.</t>
-        </is>
-      </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>&gt;50 — requiere atención</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>ONE Score SEM</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Por encima de la media (7,3)</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>&gt;7,3</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>≤7,3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>ONE Service CAM</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="D13" s="37" t="inlineStr">
-        <is>
-          <t>5-8% regular / &lt;5% mejorar</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>ONE Diferidos</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="D14" s="37" t="inlineStr">
-        <is>
-          <t>5-8% regular / &lt;5% mejorar</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t>ONE Multimedia</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>≥5</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>≥5</t>
-        </is>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>3-5 regular / &lt;3 mejorar</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/informes/informe_seguimiento_emilio_rivas_audi.xlsx
+++ b/informes/informe_seguimiento_emilio_rivas_audi.xlsx
@@ -2501,7 +2501,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fecha: 06/05/2026</t>
+          <t>Fecha: 07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2882,6 +2882,11 @@
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
@@ -2896,6 +2901,7 @@
       <c r="B56" s="9" t="inlineStr"/>
       <c r="C56" s="9" t="inlineStr"/>
       <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
@@ -2906,6 +2912,7 @@
       <c r="B57" s="13" t="inlineStr"/>
       <c r="C57" s="13" t="inlineStr"/>
       <c r="D57" s="13" t="inlineStr"/>
+      <c r="E57" s="13" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
@@ -2916,6 +2923,7 @@
       <c r="B58" s="9" t="inlineStr"/>
       <c r="C58" s="9" t="inlineStr"/>
       <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="13" t="inlineStr">
@@ -2926,6 +2934,7 @@
       <c r="B59" s="13" t="inlineStr"/>
       <c r="C59" s="13" t="inlineStr"/>
       <c r="D59" s="13" t="inlineStr"/>
+      <c r="E59" s="13" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
@@ -2936,6 +2945,7 @@
       <c r="B60" s="9" t="inlineStr"/>
       <c r="C60" s="9" t="inlineStr"/>
       <c r="D60" s="9" t="inlineStr"/>
+      <c r="E60" s="9" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="13" t="inlineStr">
@@ -2946,6 +2956,7 @@
       <c r="B61" s="13" t="inlineStr"/>
       <c r="C61" s="13" t="inlineStr"/>
       <c r="D61" s="13" t="inlineStr"/>
+      <c r="E61" s="13" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
@@ -2956,6 +2967,7 @@
       <c r="B62" s="9" t="inlineStr"/>
       <c r="C62" s="9" t="inlineStr"/>
       <c r="D62" s="9" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="13" t="inlineStr">
@@ -2966,6 +2978,7 @@
       <c r="B63" s="13" t="inlineStr"/>
       <c r="C63" s="13" t="inlineStr"/>
       <c r="D63" s="13" t="inlineStr"/>
+      <c r="E63" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -3513,7 +3526,7 @@
       </c>
       <c r="D38" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>&lt;20</t>
         </is>
       </c>
     </row>

--- a/informes/informe_seguimiento_emilio_rivas_audi.xlsx
+++ b/informes/informe_seguimiento_emilio_rivas_audi.xlsx
@@ -2473,7 +2473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2771,23 +2771,40 @@
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Sin datos registrados</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>10. ONE KVPS</t>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>PUNTOS POSITIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Medidas de Servicio (EC28): 0,00% — 2/2 pts  |  Referencia: 0pts &gt;5% | 1pt ≤5% | 2pts ≤1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Conectividad Posventa: 47,76% — 2/2 pts  |  Referencia: 0pts &lt;25% | 1pt ≥25% | 2pts ≥45%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>PUNTOS POSITIVOS</t>
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>PUNTOS A MEJORAR</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2816,7 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Instalación ONE: Rivas Audi (00158)</t>
+          <t>Satisfacción General (CEM Q4): 4,69 — 1/2 pts  |  Referencia: 0pts &lt;4,60 | 1pt ≥4,60 | 2pts ≥4,80</t>
         </is>
       </c>
     </row>
@@ -2811,38 +2828,21 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Service CAM Acum.: 13% (media equipo: 8%; bueno ≥8%) — en rango positivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Diferidos Acum.: 30% (media equipo: 16%; bueno ≥8%) — en rango positivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>Multimedia Acum.: 6,8 (media equipo: 6,2; bueno ≥5) — en rango positivo</t>
+          <t>Información Proceso (TRS): 62,50% — 0/2 pts  |  Referencia: 0pts &lt;80% | 1pt ≥80% | 2pts ≥90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>10. ONE KVPS</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>PUNTOS A MEJORAR</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>PUNTOS POSITIVOS</t>
         </is>
       </c>
     </row>
@@ -2854,144 +2854,201 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
+          <t>Instalación ONE: Rivas Audi (00158)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>Service CAM Acum.: 13% (media equipo: 8%; bueno ≥8%) — en rango positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Diferidos Acum.: 30% (media equipo: 16%; bueno ≥8%) — en rango positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>Multimedia Acum.: 6,8 (media equipo: 6,2; bueno ≥5) — en rango positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>PUNTOS A MEJORAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
           <t>Score SEM: 6,8 (media equipo: 7,3) — por debajo de la media</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>11. Tareas pendientes</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Fecha límite</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Utilizar el Laser de desgaste</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr"/>
-      <c r="C56" s="9" t="inlineStr"/>
-      <c r="D56" s="9" t="inlineStr"/>
-      <c r="E56" s="9" t="inlineStr"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Puntos de Calidad</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr"/>
-      <c r="C57" s="13" t="inlineStr"/>
-      <c r="D57" s="13" t="inlineStr"/>
-      <c r="E57" s="13" t="inlineStr"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr"/>
+      <c r="C62" s="13" t="inlineStr"/>
+      <c r="D62" s="13" t="inlineStr"/>
+      <c r="E62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>Indice de reclamaciones a clientes</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr"/>
-      <c r="C58" s="9" t="inlineStr"/>
-      <c r="D58" s="9" t="inlineStr"/>
-      <c r="E58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr"/>
+      <c r="C63" s="9" t="inlineStr"/>
+      <c r="D63" s="9" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>Productividad</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr"/>
-      <c r="C59" s="13" t="inlineStr"/>
-      <c r="D59" s="13" t="inlineStr"/>
-      <c r="E59" s="13" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr"/>
+      <c r="C64" s="13" t="inlineStr"/>
+      <c r="D64" s="13" t="inlineStr"/>
+      <c r="E64" s="13" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Ocupación Platon</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr"/>
-      <c r="C60" s="9" t="inlineStr"/>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="9" t="inlineStr"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Mantenimientos &lt;24h</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr"/>
-      <c r="C61" s="13" t="inlineStr"/>
-      <c r="D61" s="13" t="inlineStr"/>
-      <c r="E61" s="13" t="inlineStr"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr"/>
+      <c r="C66" s="13" t="inlineStr"/>
+      <c r="D66" s="13" t="inlineStr"/>
+      <c r="E66" s="13" t="inlineStr"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Score One.</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr"/>
-      <c r="C62" s="9" t="inlineStr"/>
-      <c r="D62" s="9" t="inlineStr"/>
-      <c r="E62" s="9" t="inlineStr"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr"/>
+      <c r="C67" s="9" t="inlineStr"/>
+      <c r="D67" s="9" t="inlineStr"/>
+      <c r="E67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>Service Cam</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr"/>
-      <c r="C63" s="13" t="inlineStr"/>
-      <c r="D63" s="13" t="inlineStr"/>
-      <c r="E63" s="13" t="inlineStr"/>
+      <c r="B68" s="13" t="inlineStr"/>
+      <c r="C68" s="13" t="inlineStr"/>
+      <c r="D68" s="13" t="inlineStr"/>
+      <c r="E68" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="48">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A54:F54"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B54:F54"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
@@ -3004,8 +3061,11 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B10:F10"/>
@@ -3014,15 +3074,15 @@
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -3586,10 +3646,8 @@
       <c r="B43" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C43" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="D43" s="28" t="inlineStr">
         <is>
